--- a/research/traditional_assets/database/data/hungary/hungary_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,119 +587,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D2">
-        <v>21.8285</v>
+      <c r="E2">
+        <v>2.531</v>
       </c>
       <c r="G2">
-        <v>0.006966524954449645</v>
+        <v>0.03405881375643795</v>
       </c>
       <c r="H2">
-        <v>0.006966524954449645</v>
+        <v>0.03405881375643795</v>
       </c>
       <c r="I2">
-        <v>0.01544603622592977</v>
+        <v>0.03621864097026084</v>
       </c>
       <c r="J2">
-        <v>0.01273958037940728</v>
+        <v>0.03299205645742796</v>
       </c>
       <c r="K2">
-        <v>7.214</v>
+        <v>15.4</v>
       </c>
       <c r="L2">
-        <v>0.01288628487728199</v>
+        <v>0.02558564545605583</v>
       </c>
       <c r="M2">
-        <v>0.675</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.003738990749459924</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.09356806210146937</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.675</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.003738990749459924</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.09356806210146937</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>113.563</v>
+        <v>53.47</v>
       </c>
       <c r="V2">
-        <v>0.6290533429346923</v>
+        <v>0.3943215339233038</v>
       </c>
       <c r="W2">
-        <v>0.01549865229110512</v>
+        <v>0.2005208333333333</v>
       </c>
       <c r="X2">
-        <v>0.08754891652001899</v>
+        <v>0.1449128254708009</v>
       </c>
       <c r="Y2">
-        <v>-0.07205026422891388</v>
+        <v>0.05560800786253248</v>
       </c>
       <c r="Z2">
-        <v>3.751868159854166</v>
+        <v>4.208561160133689</v>
       </c>
       <c r="AA2">
-        <v>0.0873118312852736</v>
+        <v>0.06929619232401862</v>
       </c>
       <c r="AB2">
-        <v>0.06491062146385032</v>
+        <v>0.1019829348033185</v>
       </c>
       <c r="AC2">
-        <v>0.02240120982142328</v>
+        <v>-0.03268674247929992</v>
       </c>
       <c r="AD2">
-        <v>219</v>
+        <v>128.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>219</v>
+        <v>128.7</v>
       </c>
       <c r="AG2">
-        <v>105.437</v>
+        <v>75.22999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5481440692814057</v>
+        <v>0.4869466515323496</v>
       </c>
       <c r="AI2">
-        <v>0.6283083014158454</v>
+        <v>0.5826165685830693</v>
       </c>
       <c r="AJ2">
-        <v>0.368703381858746</v>
+        <v>0.3568277759332163</v>
       </c>
       <c r="AK2">
-        <v>0.4486833594335126</v>
+        <v>0.4493221047601982</v>
       </c>
       <c r="AL2">
-        <v>3.65</v>
+        <v>2.63</v>
       </c>
       <c r="AM2">
-        <v>3.601</v>
+        <v>1.52</v>
       </c>
       <c r="AN2">
-        <v>12.71038885664539</v>
+        <v>4.714285714285714</v>
       </c>
       <c r="AO2">
-        <v>2.369041095890411</v>
+        <v>8.288973384030419</v>
       </c>
       <c r="AP2">
-        <v>6.119384793964016</v>
+        <v>2.755677655677655</v>
       </c>
       <c r="AQ2">
-        <v>2.401277422938073</v>
+        <v>14.3421052631579</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Elso Hazai Energia-portfolió Nyilvánosan Muködo Részvénytársaság (BUSE:EHEP)</t>
+          <t>AutoWallis Nyilvánosan Muködo Részvénytársaság (BUSE:AUTOWALLIS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,8 +715,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="E3">
+        <v>2.531</v>
+      </c>
+      <c r="G3">
+        <v>0.03405881375643795</v>
+      </c>
+      <c r="H3">
+        <v>0.03405881375643795</v>
+      </c>
+      <c r="I3">
+        <v>0.03621864097026084</v>
+      </c>
+      <c r="J3">
+        <v>0.02976547194459508</v>
+      </c>
       <c r="K3">
-        <v>-0.046</v>
+        <v>15.4</v>
+      </c>
+      <c r="L3">
+        <v>0.02558564545605583</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -728,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -737,67 +752,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.063</v>
+        <v>50.6</v>
       </c>
       <c r="V3">
-        <v>0.02307692307692308</v>
+        <v>0.4501779359430605</v>
       </c>
       <c r="W3">
-        <v>-1.483870967741935</v>
+        <v>0.4010416666666667</v>
       </c>
       <c r="X3">
-        <v>0.05741399390453115</v>
+        <v>0.1319304528576662</v>
       </c>
       <c r="Y3">
-        <v>-1.541284961646467</v>
+        <v>0.2691112138090005</v>
       </c>
       <c r="Z3">
-        <v>-0</v>
+        <v>4.656146050901214</v>
       </c>
       <c r="AA3">
-        <v>5.875</v>
+        <v>0.1385923846480372</v>
       </c>
       <c r="AB3">
-        <v>0.05741399390453115</v>
+        <v>0.1007150863041062</v>
       </c>
       <c r="AC3">
-        <v>5.817586006095468</v>
+        <v>0.03787729834393108</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="AG3">
-        <v>-0.063</v>
+        <v>45.6</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.461169702780441</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.5596276905177429</v>
       </c>
       <c r="AJ3">
-        <v>-0.02362204724409449</v>
+        <v>0.2886075949367088</v>
       </c>
       <c r="AK3">
-        <v>7.875</v>
+        <v>0.3759274525968673</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.52</v>
+      </c>
+      <c r="AN3">
+        <v>3.523809523809524</v>
+      </c>
+      <c r="AO3">
+        <v>8.288973384030419</v>
+      </c>
+      <c r="AP3">
+        <v>1.67032967032967</v>
+      </c>
+      <c r="AQ3">
+        <v>14.3421052631579</v>
       </c>
     </row>
     <row r="4">
@@ -808,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AutoWallis Nyilvánosan Muködo Részvénytársaság (BUSE:AUTOWALLIS)</t>
+          <t>AKKO Invest Nyrt. (BUSE:AKKO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -816,26 +843,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D4">
-        <v>43.33</v>
-      </c>
-      <c r="G4">
-        <v>0.004974674384949349</v>
-      </c>
-      <c r="H4">
-        <v>0.004974674384949349</v>
-      </c>
-      <c r="I4">
-        <v>0.01503256150506512</v>
-      </c>
-      <c r="J4">
-        <v>0.01032010683100539</v>
-      </c>
       <c r="K4">
-        <v>6.11</v>
-      </c>
-      <c r="L4">
-        <v>0.01105282199710565</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -843,220 +852,71 @@
       <c r="N4">
         <v>-0</v>
       </c>
-      <c r="O4">
-        <v>-0</v>
-      </c>
       <c r="P4">
         <v>-0</v>
       </c>
       <c r="Q4">
         <v>-0</v>
       </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>41.3</v>
+        <v>2.87</v>
       </c>
       <c r="V4">
-        <v>0.2640664961636828</v>
+        <v>0.1237068965517241</v>
       </c>
       <c r="W4">
-        <v>0.2951690821256039</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.08754891652001899</v>
+        <v>0.1578951980839355</v>
       </c>
       <c r="Y4">
-        <v>0.2076201656055849</v>
+        <v>-0.1578951980839355</v>
       </c>
       <c r="Z4">
-        <v>8.460361187633916</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>0.0873118312852736</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06491062146385032</v>
+        <v>0.1032507833025309</v>
       </c>
       <c r="AC4">
-        <v>0.02240120982142328</v>
+        <v>-0.1032507833025309</v>
       </c>
       <c r="AD4">
-        <v>122.4</v>
+        <v>32.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>122.4</v>
+        <v>32.5</v>
       </c>
       <c r="AG4">
-        <v>81.10000000000001</v>
+        <v>29.63</v>
       </c>
       <c r="AH4">
-        <v>0.4390243902439024</v>
+        <v>0.5834829443447037</v>
       </c>
       <c r="AI4">
-        <v>0.7391304347826086</v>
+        <v>0.6632653061224489</v>
       </c>
       <c r="AJ4">
-        <v>0.3414736842105264</v>
+        <v>0.5608555744841945</v>
       </c>
       <c r="AK4">
-        <v>0.6524537409493162</v>
+        <v>0.6423151961846955</v>
       </c>
       <c r="AL4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.991</v>
-      </c>
-      <c r="AN4">
-        <v>8.214765100671141</v>
-      </c>
-      <c r="AO4">
-        <v>7.990384615384616</v>
-      </c>
-      <c r="AP4">
-        <v>5.442953020134229</v>
-      </c>
-      <c r="AQ4">
-        <v>8.385469223007064</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Hungary</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Forrás nyRt. (BUSE:FORRAS/T)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.327</v>
-      </c>
-      <c r="G5">
-        <v>0.1638176638176638</v>
-      </c>
-      <c r="H5">
-        <v>0.1638176638176638</v>
-      </c>
-      <c r="I5">
-        <v>0.05470085470085471</v>
-      </c>
-      <c r="J5">
-        <v>0.04309458479200177</v>
-      </c>
-      <c r="K5">
-        <v>1.15</v>
-      </c>
-      <c r="L5">
-        <v>0.1638176638176638</v>
-      </c>
-      <c r="M5">
-        <v>0.675</v>
-      </c>
-      <c r="N5">
-        <v>0.03154205607476636</v>
-      </c>
-      <c r="O5">
-        <v>0.5869565217391305</v>
-      </c>
-      <c r="P5">
-        <v>0.675</v>
-      </c>
-      <c r="Q5">
-        <v>0.03154205607476636</v>
-      </c>
-      <c r="R5">
-        <v>0.5869565217391305</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>72.2</v>
-      </c>
-      <c r="V5">
-        <v>3.373831775700935</v>
-      </c>
-      <c r="W5">
-        <v>0.01549865229110512</v>
-      </c>
-      <c r="X5">
-        <v>0.2312295989592842</v>
-      </c>
-      <c r="Y5">
-        <v>-0.2157309466681791</v>
-      </c>
-      <c r="Z5">
-        <v>0.08369198488298621</v>
-      </c>
-      <c r="AA5">
-        <v>0.003606671338950779</v>
-      </c>
-      <c r="AB5">
-        <v>0.07483299652246937</v>
-      </c>
-      <c r="AC5">
-        <v>-0.0712263251835186</v>
-      </c>
-      <c r="AD5">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="AG5">
-        <v>24.39999999999999</v>
-      </c>
-      <c r="AH5">
-        <v>0.8186440677966101</v>
-      </c>
-      <c r="AI5">
-        <v>0.5281574630945872</v>
-      </c>
-      <c r="AJ5">
-        <v>0.5327510917030567</v>
-      </c>
-      <c r="AK5">
-        <v>0.2204155374887082</v>
-      </c>
-      <c r="AL5">
-        <v>2.61</v>
-      </c>
-      <c r="AM5">
-        <v>2.61</v>
-      </c>
-      <c r="AN5">
-        <v>41.45922746781115</v>
-      </c>
-      <c r="AO5">
-        <v>0.1471264367816092</v>
-      </c>
-      <c r="AP5">
-        <v>10.47210300429184</v>
-      </c>
-      <c r="AQ5">
-        <v>0.1471264367816092</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hungary/hungary_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,26 +587,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.7150000000000001</v>
+      </c>
       <c r="E2">
-        <v>2.531</v>
+        <v>0.28645</v>
       </c>
       <c r="G2">
-        <v>0.03405881375643795</v>
+        <v>0.04104065827686351</v>
       </c>
       <c r="H2">
-        <v>0.03405881375643795</v>
+        <v>0.04104065827686351</v>
       </c>
       <c r="I2">
-        <v>0.03621864097026084</v>
+        <v>0.0473620522749274</v>
       </c>
       <c r="J2">
-        <v>0.03299205645742796</v>
+        <v>0.0398048701090509</v>
       </c>
       <c r="K2">
-        <v>15.4</v>
+        <v>32.369</v>
       </c>
       <c r="L2">
-        <v>0.02558564545605583</v>
+        <v>0.03133494675701839</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>53.47</v>
+        <v>66.783</v>
       </c>
       <c r="V2">
-        <v>0.3943215339233038</v>
+        <v>0.3520453347390617</v>
       </c>
       <c r="W2">
-        <v>0.2005208333333333</v>
+        <v>0.1703030303030303</v>
       </c>
       <c r="X2">
-        <v>0.1449128254708009</v>
+        <v>0.1276272971839221</v>
       </c>
       <c r="Y2">
-        <v>0.05560800786253248</v>
+        <v>0.04267573311910819</v>
       </c>
       <c r="Z2">
-        <v>4.208561160133689</v>
+        <v>6.920345682320625</v>
       </c>
       <c r="AA2">
-        <v>0.06929619232401862</v>
+        <v>0.1142023202541934</v>
       </c>
       <c r="AB2">
-        <v>0.1019829348033185</v>
+        <v>0.08710549695528891</v>
       </c>
       <c r="AC2">
-        <v>-0.03268674247929992</v>
+        <v>0.02709227424340237</v>
       </c>
       <c r="AD2">
-        <v>128.7</v>
+        <v>280</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>128.7</v>
+        <v>280</v>
       </c>
       <c r="AG2">
-        <v>75.22999999999999</v>
+        <v>213.217</v>
       </c>
       <c r="AH2">
-        <v>0.4869466515323496</v>
+        <v>0.5961251862891207</v>
       </c>
       <c r="AI2">
-        <v>0.5826165685830693</v>
+        <v>0.6361959119868399</v>
       </c>
       <c r="AJ2">
-        <v>0.3568277759332163</v>
+        <v>0.529183429837907</v>
       </c>
       <c r="AK2">
-        <v>0.4493221047601982</v>
+        <v>0.5711174742120305</v>
       </c>
       <c r="AL2">
-        <v>2.63</v>
+        <v>13.21</v>
       </c>
       <c r="AM2">
-        <v>1.52</v>
+        <v>10.609</v>
       </c>
       <c r="AN2">
-        <v>4.714285714285714</v>
+        <v>4.685800351435026</v>
       </c>
       <c r="AO2">
-        <v>8.288973384030419</v>
+        <v>3.703633610900833</v>
       </c>
       <c r="AP2">
-        <v>2.755677655677655</v>
+        <v>3.568186762614007</v>
       </c>
       <c r="AQ2">
-        <v>14.3421052631579</v>
+        <v>4.611650485436894</v>
       </c>
     </row>
     <row r="3">
@@ -715,26 +718,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.34</v>
+      </c>
       <c r="E3">
-        <v>2.531</v>
+        <v>0.476</v>
       </c>
       <c r="G3">
-        <v>0.03405881375643795</v>
+        <v>0.03862157260215513</v>
       </c>
       <c r="H3">
-        <v>0.03405881375643795</v>
+        <v>0.03862157260215513</v>
       </c>
       <c r="I3">
-        <v>0.03621864097026084</v>
+        <v>0.04662327963298837</v>
       </c>
       <c r="J3">
-        <v>0.02976547194459508</v>
+        <v>0.03943552402290267</v>
       </c>
       <c r="K3">
-        <v>15.4</v>
+        <v>29.6</v>
       </c>
       <c r="L3">
-        <v>0.02558564545605583</v>
+        <v>0.03158007041502187</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>50.6</v>
+        <v>58.9</v>
       </c>
       <c r="V3">
-        <v>0.4501779359430605</v>
+        <v>0.3567534827377347</v>
       </c>
       <c r="W3">
-        <v>0.4010416666666667</v>
+        <v>0.4060356652949245</v>
       </c>
       <c r="X3">
-        <v>0.1319304528576662</v>
+        <v>0.1276272971839221</v>
       </c>
       <c r="Y3">
-        <v>0.2691112138090005</v>
+        <v>0.2784083681110024</v>
       </c>
       <c r="Z3">
-        <v>4.656146050901214</v>
+        <v>7.940528634361231</v>
       </c>
       <c r="AA3">
-        <v>0.1385923846480372</v>
+        <v>0.3131389077148989</v>
       </c>
       <c r="AB3">
-        <v>0.1007150863041062</v>
+        <v>0.08710549695528891</v>
       </c>
       <c r="AC3">
-        <v>0.03787729834393108</v>
+        <v>0.22603341075961</v>
       </c>
       <c r="AD3">
-        <v>96.2</v>
+        <v>245.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>96.2</v>
+        <v>245.6</v>
       </c>
       <c r="AG3">
-        <v>45.6</v>
+        <v>186.7</v>
       </c>
       <c r="AH3">
-        <v>0.461169702780441</v>
+        <v>0.5980034088142197</v>
       </c>
       <c r="AI3">
-        <v>0.5596276905177429</v>
+        <v>0.6409185803757829</v>
       </c>
       <c r="AJ3">
-        <v>0.2886075949367088</v>
+        <v>0.5306992609437181</v>
       </c>
       <c r="AK3">
-        <v>0.3759274525968673</v>
+        <v>0.5757015109466543</v>
       </c>
       <c r="AL3">
-        <v>2.63</v>
+        <v>11.7</v>
       </c>
       <c r="AM3">
-        <v>1.52</v>
+        <v>9.1</v>
       </c>
       <c r="AN3">
-        <v>3.523809523809524</v>
+        <v>4.660341555977229</v>
       </c>
       <c r="AO3">
-        <v>8.288973384030419</v>
+        <v>3.735042735042736</v>
       </c>
       <c r="AP3">
-        <v>1.67032967032967</v>
+        <v>3.5426944971537</v>
       </c>
       <c r="AQ3">
-        <v>14.3421052631579</v>
+        <v>4.802197802197803</v>
       </c>
     </row>
     <row r="4">
@@ -843,8 +849,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>1.09</v>
+      </c>
+      <c r="E4">
+        <v>0.0969</v>
+      </c>
+      <c r="G4">
+        <v>0.06530825496342738</v>
+      </c>
+      <c r="H4">
+        <v>0.06530825496342738</v>
+      </c>
+      <c r="I4">
+        <v>0.05517241379310345</v>
+      </c>
+      <c r="J4">
+        <v>0.03726790450928381</v>
+      </c>
       <c r="K4">
-        <v>0</v>
+        <v>2.81</v>
+      </c>
+      <c r="L4">
+        <v>0.02936259143155695</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -852,71 +879,187 @@
       <c r="N4">
         <v>-0</v>
       </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
       <c r="P4">
         <v>-0</v>
       </c>
       <c r="Q4">
         <v>-0</v>
       </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.87</v>
+        <v>7.87</v>
       </c>
       <c r="V4">
-        <v>0.1237068965517241</v>
+        <v>0.3406926406926407</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>0.1703030303030303</v>
       </c>
       <c r="X4">
-        <v>0.1578951980839355</v>
+        <v>0.127682046804463</v>
       </c>
       <c r="Y4">
-        <v>-0.1578951980839355</v>
+        <v>0.04262098349856736</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.064361191162344</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.1142023202541934</v>
       </c>
       <c r="AB4">
-        <v>0.1032507833025309</v>
+        <v>0.08711004601079106</v>
       </c>
       <c r="AC4">
-        <v>-0.1032507833025309</v>
+        <v>0.02709227424340237</v>
       </c>
       <c r="AD4">
-        <v>32.5</v>
+        <v>34.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>32.5</v>
+        <v>34.4</v>
       </c>
       <c r="AG4">
-        <v>29.63</v>
+        <v>26.53</v>
       </c>
       <c r="AH4">
-        <v>0.5834829443447037</v>
+        <v>0.5982608695652174</v>
       </c>
       <c r="AI4">
-        <v>0.6632653061224489</v>
+        <v>0.6067019400352733</v>
       </c>
       <c r="AJ4">
-        <v>0.5608555744841945</v>
+        <v>0.5345557122708039</v>
       </c>
       <c r="AK4">
-        <v>0.6423151961846955</v>
+        <v>0.5433135367601883</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.51</v>
+      </c>
+      <c r="AN4">
+        <v>4.838255977496483</v>
+      </c>
+      <c r="AO4">
+        <v>3.496688741721854</v>
+      </c>
+      <c r="AP4">
+        <v>3.731364275668072</v>
+      </c>
+      <c r="AQ4">
+        <v>3.496688741721854</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Amixa Holding Nyilvánosan Muködo Részvénytársaság (BUSE:AMIXA)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>-0.041</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.013</v>
+      </c>
+      <c r="V5">
+        <v>0.008666666666666666</v>
+      </c>
+      <c r="W5">
+        <v>-1.708333333333333</v>
+      </c>
+      <c r="X5">
+        <v>0.0765394177116222</v>
+      </c>
+      <c r="Y5">
+        <v>-1.784872751044956</v>
+      </c>
+      <c r="AB5">
+        <v>0.0765394177116222</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-0.013</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.008742434431741761</v>
+      </c>
+      <c r="AK5">
+        <v>-0.06403940886699508</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>-0.001</v>
+      </c>
+      <c r="AN5">
+        <v>-0</v>
+      </c>
+      <c r="AP5">
+        <v>0.2363636363636364</v>
+      </c>
+      <c r="AQ5">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
